--- a/output/interpretation_high_attention_cluster_MKM_MKMonVAE/centroidi_annotated_21_risk1_2024_pr_interpretation_high_attention_MKM.xlsx
+++ b/output/interpretation_high_attention_cluster_MKM_MKMonVAE/centroidi_annotated_21_risk1_2024_pr_interpretation_high_attention_MKM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lavoro\07Massaciuccoli\risk_assessment\r_scripts\r_03UnsupervisedRiskAssessment\output\MultiKmeans\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lavoro\github\TerrestrialEcosystemRiskAssessment\output\interpretation_high_attention_cluster_MKM_MKMonVAE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4362E1EE-2D74-4CC4-ACE6-30954B981A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA203419-E297-4946-84DB-82B48DB1D96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34260" yWindow="-6840" windowWidth="28800" windowHeight="15460" firstSheet="1" activeTab="3" xr2:uid="{22D72F45-BD53-46FD-A559-98F644819B2D}"/>
+    <workbookView xWindow="-38510" yWindow="-11090" windowWidth="38620" windowHeight="21220" firstSheet="1" activeTab="3" xr2:uid="{22D72F45-BD53-46FD-A559-98F644819B2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="175">
   <si>
     <t>centroid_id</t>
   </si>
@@ -564,6 +564,9 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>closer attention</t>
   </si>
 </sst>
 </file>
@@ -7995,7 +7998,7 @@
         <v>25</v>
       </c>
       <c r="AO2" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="AQ2" s="7"/>
     </row>
@@ -8144,7 +8147,7 @@
         <v>25</v>
       </c>
       <c r="AO3" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:43" hidden="1" x14ac:dyDescent="0.35">
@@ -8268,7 +8271,7 @@
         <v>24</v>
       </c>
       <c r="AO4" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.35">
@@ -8406,7 +8409,7 @@
         <v>24</v>
       </c>
       <c r="AO5" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:43" hidden="1" x14ac:dyDescent="0.35">
@@ -8530,7 +8533,7 @@
         <v>24</v>
       </c>
       <c r="AO6" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:43" hidden="1" x14ac:dyDescent="0.35">
@@ -8654,7 +8657,7 @@
         <v>24</v>
       </c>
       <c r="AO7" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:43" hidden="1" x14ac:dyDescent="0.35">
@@ -8778,7 +8781,7 @@
         <v>24</v>
       </c>
       <c r="AO8" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:43" hidden="1" x14ac:dyDescent="0.35">
@@ -8902,7 +8905,7 @@
         <v>25</v>
       </c>
       <c r="AO9" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:43" hidden="1" x14ac:dyDescent="0.35">
@@ -9026,7 +9029,7 @@
         <v>24</v>
       </c>
       <c r="AO10" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:43" hidden="1" x14ac:dyDescent="0.35">
@@ -9150,7 +9153,7 @@
         <v>25</v>
       </c>
       <c r="AO11" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.35">
@@ -9277,7 +9280,7 @@
         <v>24</v>
       </c>
       <c r="AO12" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:43" hidden="1" x14ac:dyDescent="0.35">
@@ -9401,7 +9404,7 @@
         <v>24</v>
       </c>
       <c r="AO13" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.35">
@@ -9528,7 +9531,7 @@
         <v>25</v>
       </c>
       <c r="AO14" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.35">
@@ -9655,7 +9658,7 @@
         <v>25</v>
       </c>
       <c r="AO15" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.35">
@@ -9782,7 +9785,7 @@
         <v>24</v>
       </c>
       <c r="AO16" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.35">
@@ -10032,7 +10035,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO16" xr:uid="{D3A0CA49-E212-4387-8F38-D8F3AAFD7014}">
+  <autoFilter ref="A1:AO16" xr:uid="{B34CE322-D89B-4F00-9443-2053ECD3231D}">
     <filterColumn colId="3">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
